--- a/exploratory_data_analysis/normalization/risultati/statistiche_descrittive.xlsx
+++ b/exploratory_data_analysis/normalization/risultati/statistiche_descrittive.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>gdp-pop-urban_merged</t>
+          <t>gdp_pop_urban_merged</t>
         </is>
       </c>
     </row>
@@ -565,28 +565,28 @@
         <v>0.02868790198811602</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.01755305032840954</v>
+        <v>2.475556005694149</v>
       </c>
       <c r="F3" t="n">
         <v>0.04949192926291828</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5253052039019976</v>
+        <v>0.7048610245645277</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01275752971906834</v>
+        <v>0.01275754047808045</v>
       </c>
       <c r="I3" t="n">
-        <v>108.1126096491228</v>
+        <v>0.4654470863229462</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3100346973618169</v>
+        <v>0.6398084817995293</v>
       </c>
       <c r="K3" t="n">
         <v>-0.434305894455277</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.1051636960224927</v>
+        <v>6.725080162906959</v>
       </c>
       <c r="M3" t="n">
         <v>0.7669533450485546</v>
@@ -595,7 +595,7 @@
         <v>0.1445258207495332</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5687745707978733</v>
+        <v>0.5687745778311922</v>
       </c>
     </row>
     <row r="4">
@@ -614,28 +614,28 @@
         <v>0.6758574937639199</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6410227286689187</v>
+        <v>1.000182798648817</v>
       </c>
       <c r="F4" t="n">
         <v>0.7177171554699632</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7453969089978939</v>
+        <v>1.000182798648817</v>
       </c>
       <c r="H4" t="n">
-        <v>0.56870152734474</v>
+        <v>0.5687015253253199</v>
       </c>
       <c r="I4" t="n">
-        <v>2019.256884673575</v>
+        <v>1.225390509752524</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4700761374440798</v>
+        <v>1.000182798648817</v>
       </c>
       <c r="K4" t="n">
         <v>0.7728073255540938</v>
       </c>
       <c r="L4" t="n">
-        <v>0.895016468099223</v>
+        <v>1.000182798648817</v>
       </c>
       <c r="M4" t="n">
         <v>2.096679500765967</v>
@@ -644,7 +644,7 @@
         <v>0.6048408488550653</v>
       </c>
       <c r="O4" t="n">
-        <v>1.133905857847534</v>
+        <v>1.133905872665341</v>
       </c>
     </row>
     <row r="5">
@@ -663,7 +663,7 @@
         <v>-1.975753975960499</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.57783894951503</v>
+        <v>0.04105393391733923</v>
       </c>
       <c r="F5" t="n">
         <v>-1.491698842407455</v>
@@ -672,19 +672,19 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.262995429415912</v>
+        <v>-1.262995367947092</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>-3.568235684758833</v>
       </c>
       <c r="L5" t="n">
-        <v>-3.592856995736442</v>
+        <v>2.827575513919984</v>
       </c>
       <c r="M5" t="n">
         <v>-0.6291031890723228</v>
@@ -693,7 +693,7 @@
         <v>-0.6759501735656157</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2726798037716645</v>
+        <v>-0.2726798030937422</v>
       </c>
     </row>
     <row r="6">
@@ -712,7 +712,7 @@
         <v>-0.4659013701873879</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5041734531989073</v>
+        <v>1.71628596723711</v>
       </c>
       <c r="F6" t="n">
         <v>-0.4884358951939276</v>
@@ -721,19 +721,19 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4630105834133117</v>
+        <v>-0.4630105751974706</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>-0.905870685627741</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5359449284715501</v>
+        <v>6.243681223297148</v>
       </c>
       <c r="M6" t="n">
         <v>-0.2726231080661094</v>
@@ -742,7 +742,7 @@
         <v>-0.3684048501006381</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1961190340532813</v>
+        <v>-0.1961190336035212</v>
       </c>
     </row>
     <row r="7">
@@ -761,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1.50080685726306e-16</v>
+        <v>2.502943905291837</v>
       </c>
       <c r="F7" t="n">
         <v>-2.113110034174248e-16</v>
@@ -776,13 +776,13 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>6.842600815937413</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -810,28 +810,28 @@
         <v>0.534098629812612</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4958265468010926</v>
+        <v>3.276578216855933</v>
       </c>
       <c r="F8" t="n">
         <v>0.5115641048060722</v>
       </c>
       <c r="G8" t="n">
-        <v>1.016391396364886</v>
+        <v>1.363806556034006</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5369894165866882</v>
+        <v>0.5369894248025293</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>1.691052000626001</v>
       </c>
       <c r="K8" t="n">
         <v>0.09412931437225908</v>
       </c>
       <c r="L8" t="n">
-        <v>0.46405507152845</v>
+        <v>7.361183341188833</v>
       </c>
       <c r="M8" t="n">
         <v>0.7273768919338909</v>
@@ -840,7 +840,7 @@
         <v>0.6315951498993618</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8038809659467187</v>
+        <v>0.8038809663964788</v>
       </c>
     </row>
     <row r="9">
@@ -859,28 +859,28 @@
         <v>1.78836863764289</v>
       </c>
       <c r="E9" t="n">
-        <v>1.47038919903107</v>
+        <v>4.797180727742201</v>
       </c>
       <c r="F9" t="n">
         <v>4.327048321695479</v>
       </c>
       <c r="G9" t="n">
-        <v>3.892927630578497</v>
+        <v>5.223578479449142</v>
       </c>
       <c r="H9" t="n">
-        <v>1.432710506846674</v>
+        <v>1.432710565685036</v>
       </c>
       <c r="I9" t="n">
-        <v>103215.4</v>
+        <v>7.791347927064578</v>
       </c>
       <c r="J9" t="n">
-        <v>1.071806700588617</v>
+        <v>3.766131996926475</v>
       </c>
       <c r="K9" t="n">
         <v>0.3500094728868549</v>
       </c>
       <c r="L9" t="n">
-        <v>2.19431937550205</v>
+        <v>9.294757365391712</v>
       </c>
       <c r="M9" t="n">
         <v>18.04337229932958</v>
@@ -889,7 +889,7 @@
         <v>1.300406345020206</v>
       </c>
       <c r="O9" t="n">
-        <v>3.311842105734687</v>
+        <v>3.311842167165813</v>
       </c>
     </row>
   </sheetData>
